--- a/job_tracker/job_search_tracker.xlsx
+++ b/job_tracker/job_search_tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n0308g\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18568651-A530-40DE-9137-B90BBBBE4104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809B96C2-75E5-49F5-B903-260ABE42F6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="240" windowWidth="21600" windowHeight="20970" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="138">
   <si>
     <t>Job Search Tracker — How to Use</t>
   </si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>Verbal offer given July 30th. 129k and 10k sign-on bonus. Negotiated for 135k, and it's been about 1 month since then.  Didn't work out to 135k. Offer accepted at 129k with the 10k sign on bonus. Tenative start state September 21st, 2026.</t>
+  </si>
+  <si>
+    <t>Rejected by email on 9/14.</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1192,7 @@
         <v>46212</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>113</v>
@@ -1213,7 +1216,9 @@
         <v>73</v>
       </c>
       <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="O3" s="15" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="232" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
@@ -1320,7 +1325,7 @@
         <v>46211</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>73</v>
@@ -6791,7 +6796,7 @@
       </c>
       <c r="B6" s="8">
         <f>COUNTIF('Job Tracker'!F3:F301,"Applied")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>45</v>
@@ -6871,7 +6876,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF('Job Tracker'!F3:F301,"Rejected")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>63</v>
